--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_076_Brazil_mainland.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_076_Brazil_mainland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rdf2226186fe04b64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R906145f293824552"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rc7ffc4e24e0b41bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R490ea0ea86474248"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R03f5cf5cbfeb4b44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R77ef21c7a6334db8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R20cab544d0dd434e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rb2b4a923b0e6406a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rf580b60a4d08401f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R7fbb66f7954a48e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R7ed1c97e50db40bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rd9a063123685476d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ076CommercialTable" displayName="EEZ076CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ076CommercialTable" displayName="EEZ076CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ076FunctionalTable" displayName="EEZ076FunctionalTable" ref="A1:O25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O25"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ076FunctionalTable" displayName="EEZ076FunctionalTable" ref="A1:E25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E25"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ076ValidationTable" displayName="EEZ076ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ076ValidationTable" displayName="EEZ076ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -19052,7 +19006,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4cb328f459b41aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra631b2bcd2db4f5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19062,20 +19016,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -19083,660 +19027,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>5196.9037109835</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.735290060339056</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>54.36132833949548</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>5196.9037109835</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>95.75082162911798</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$275,A2,'Species'!$U$2:$U$275))</x:f>
-        <x:v>497607.8002540824</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.735290060339056</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>54.36132833949548</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>282510.58898151654</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>215097.21127256588</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.7613775187967866</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.7613775187967866</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>9844.4945104906</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.904573524987479</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>802.7374508451829</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>9844.4945104906</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>871.926661548373</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$275,A3,'Species'!$U$2:$U$275))</x:f>
-        <x:v>8583677.233163353</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.904573524987479</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>802.7374508451829</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>7902544.428210622</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>681132.8049527314</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0861915818557393</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.08619158185573918</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>46215.9448781056</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.845014812367079</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>69.98658657352694</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>46215.9448781056</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>98.27311624023015</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$275,A4,'Species'!$U$2:$U$275))</x:f>
-        <x:v>4541784.923158141</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.845014812367079</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>69.98658657352694</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>3234496.227288886</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1307288.6958692549</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.404170728300712</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.40417072830071216</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>5074.6609571516</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.343545907562977</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>220.56972796616128</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>5074.6609571516</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>228.74721413132335</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$275,A5,'Species'!$U$2:$U$275))</x:f>
-        <x:v>1160814.5566094234</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.343545907562977</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>220.56972796616128</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1119316.5868394282</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>41497.969769995194</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0370743811517806</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.037074381151780696</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>156684.62195074902</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.211663081238834</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>162.80325408175042</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>156684.62195074902</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>312.7482295157343</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$275,A6,'Species'!$U$2:$U$275))</x:f>
-        <x:v>49002838.107438914</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.211663081238834</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>162.80325408175042</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>25508766.318150803</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>23494071.78928811</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.9210195231029603</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.9210195231029603</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>11955.165390640399</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0746681614807865</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>11.875944558679679</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>11955.165390640399</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>12.268183678545524</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$275,A7,'Species'!$U$2:$U$275))</x:f>
-        <x:v>146668.16491976686</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0746681614807865</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>11.875944558679679</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>141978.88136909145</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>4689.283550675405</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0330280356166848</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.03302803561668471</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>136077.0068477063</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.538187169154539</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>345.2925189935761</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>136077.0068477063</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>533.6882228577646</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$275,A8,'Species'!$U$2:$U$275))</x:f>
-        <x:v>72622695.95635624</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.538187169154539</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>345.2925189935761</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>46986372.47155061</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>25636323.48480563</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.545611889922508</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.5456118899225079</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>405526.75004661235</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6345912414202477</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>431.11312153600517</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>405526.75004661235</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>739.9124593571723</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$275,A9,'Species'!$U$2:$U$275))</x:f>
-        <x:v>300054294.9621102</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6345912414202477</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>431.11312153600517</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>174827903.07894638</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>125226391.88316384</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.7162837835251952</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.7162837835251952</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>124.99305446509999</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.78</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>602.5595860743575</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>124.99305446509999</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>602.5595860743575</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$275,A10,'Species'!$U$2:$U$275))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>75315.76316066028</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.78</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>602.5595860743575</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>75315.76316066028</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>83512.76020118038</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.8627485061677787</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>729.03521394468</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>83512.76020118038</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>899.5356856677236</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$275,A11,'Species'!$U$2:$U$275))</x:f>
-        <x:v>75122708.00957297</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.8627485061677787</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>729.03521394468</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>60883743.000378296</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>14238965.009194672</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.2338713802320957</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.23387138023209578</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>43895.87808098191</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.437731298509538</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2739.878462556511</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>43895.87808098191</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2752.0396371349248</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$275,A12,'Species'!$U$2:$U$275))</x:f>
-        <x:v>120803196.38570435</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.437731298509538</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2739.878462556511</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>120269370.94908875</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>533825.4366156012</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.004438581763611</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.004438581763611077</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea8aa1e327eb4655"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R206483f8cb264fba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19746,20 +19261,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -19767,1362 +19272,478 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2711.5844440138003</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8017670799575187</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>633.5298465291153</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2711.5844440138003</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>649.5822579392167</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$275,A2,'Species'!$U$2:$U$275))</x:f>
-        <x:v>1761397.14573534</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8017670799575187</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>633.5298465291153</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1717869.6766667992</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>43527.469068540726</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0253380507612182</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.025338050761218124</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>601.3173101699</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.1996752152098225</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1583.7083817021235</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>601.3173101699</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1583.786169307381</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$275,A3,'Species'!$U$2:$U$275))</x:f>
-        <x:v>952358.0392122042</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.1996752152098225</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1583.7083817021235</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>952311.2641786461</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>46.77503355802037</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.000049117379283</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.00004911737928287882</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>71.3774416406</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.339192866668015</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2183.699459817115</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>71.3774416406</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2184.209062126144</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$275,A4,'Species'!$U$2:$U$275))</x:f>
-        <x:v>155903.2548627785</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.339192866668015</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2183.699459817115</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>155866.88075370586</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>36.37410907263984</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0002333665041396</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0002333665041396231</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>20055.7993694384</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.394354976035367</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2479.4478373732068</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>20055.7993694384</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2514.994042433867</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$275,A5,'Species'!$U$2:$U$275))</x:f>
-        <x:v>50440215.930386476</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.394354976035367</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2479.4478373732068</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>49727308.37334496</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>712907.5570415184</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0143363391336029</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.014336339133602778</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>32537.2669535233</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.0608620710139265</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1150.43496056688</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>32537.2669535233</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1156.421327299693</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$275,A6,'Species'!$U$2:$U$275))</x:f>
-        <x:v>37626789.437097855</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.0608620710139265</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1150.43496056688</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>37432009.42463062</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>194780.01246723533</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0052035681616138</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.005203568161613793</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>56538.26834629501</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.357880933051981</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2279.716975052677</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>56538.26834629501</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2576.330778779651</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$275,A7,'Species'!$U$2:$U$275))</x:f>
-        <x:v>145661280.91946313</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.357880933051981</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2279.716975052677</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>128891250.08913216</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>16770030.830330968</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1301099245971622</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.13010992459716225</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>36615.043896777905</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.708795357924969</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>511.4407848927553</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>36615.043896777905</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>519.272305702965</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$275,A8,'Species'!$U$2:$U$275))</x:f>
-        <x:v>19013178.26769514</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.708795357924969</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>511.4407848927553</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>18726426.78945078</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>286751.47824436054</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.015312663834293</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.015312663834293107</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>20046.891280618198</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.7383974837792273</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>547.5168430846807</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>20046.891280618198</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>824.1837459292436</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$275,A9,'Species'!$U$2:$U$275))</x:f>
-        <x:v>16522321.949896198</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.7383974837792273</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>547.5168430846807</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>10976010.627625886</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>5546311.322270311</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.5053121311955198</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.5053121311955198</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>36606.6587129027</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.093569260683483</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1240.4214300401964</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>36606.6587129027</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1423.524441995559</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$275,A10,'Species'!$U$2:$U$275))</x:f>
-        <x:v>52110473.41760669</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.093569260683483</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1240.4214300401964</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>45407683.94965219</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>6702789.4679545015</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1476135509440764</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.14761355094407635</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>11376.711947208598</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.196629033117428</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>157.26389694019153</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>11376.711947208598</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>220.33491824899474</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$275,A11,'Species'!$U$2:$U$275))</x:f>
-        <x:v>2506686.896830568</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.196629033117428</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>157.26389694019153</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1789146.0551840586</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>717540.8416465095</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.401052132981224</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.40105213298122405</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>2511.2430398082</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.49</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>3090.295432513592</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>2511.2430398082</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>3090.295432513592</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$275,A12,'Species'!$U$2:$U$275))</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>7760482.89585083</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.49</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>3090.295432513592</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
-        <x:v>7760482.89585083</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>14836.298389551099</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.983477609728249</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>962.6703807353698</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>14836.298389551099</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1015.261738976971</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$275,A13,'Species'!$U$2:$U$275))</x:f>
-        <x:v>15062726.102956882</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.983477609728249</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>962.6703807353698</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>14282465.019372711</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>780261.0835841708</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0546307015298708</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.05463070152987079</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>373058.77425563673</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.4711440814445584</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>295.89939789398363</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>373058.77425563673</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>463.3900692295801</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$275,A14,'Species'!$U$2:$U$275))</x:f>
-        <x:v>172871731.2290218</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.4711440814445584</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>295.89939789398363</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>110387866.68131047</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>62483864.54771131</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.5660392434985821</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.566039243498582</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>19792.5184047531</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.95426726180991</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>900.0512964573654</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>19792.5184047531</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>1215.290623948415</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$275,A15,'Species'!$U$2:$U$275))</x:f>
-        <x:v>24053662.041622885</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.95426726180991</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>900.0512964573654</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>17814281.850354295</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>6239380.191268589</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.3502459567936216</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.3502459567936217</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>21775.2413316368</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.8759706701602665</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>751.5721352921357</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>21775.2413316368</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>884.8253968895442</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$275,A16,'Species'!$U$2:$U$275))</x:f>
-        <x:v>19267286.553631138</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.8759706701602665</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>751.5721352921357</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>16365664.624119839</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>2901621.9295112994</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.1772993640132932</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.17729936401329324</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>11955.165390640399</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.0746681614807865</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>11.875944558679679</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>11955.165390640399</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>12.268183678545524</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$275,A17,'Species'!$U$2:$U$275))</x:f>
-        <x:v>146668.16491976686</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.0746681614807865</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>11.875944558679679</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>141978.88136909145</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>4689.283550675405</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0330280356166848</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.03302803561668471</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>34839.232930897</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.7301955879038626</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>53.72737072933404</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>34839.232930897</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>58.41397341796115</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$275,A18,'Species'!$U$2:$U$275))</x:f>
-        <x:v>2035098.0263275742</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.7301955879038626</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>53.72737072933404</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>1871820.383603926</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>163277.6427236481</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0872293325544837</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.0872293325544837</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>2128.7564434947</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.2369846853861706</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>172.57770344938686</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>2128.7564434947</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>537.3316842419138</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$275,A19,'Species'!$U$2:$U$275))</x:f>
-        <x:v>1143848.2851238335</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.2369846853861706</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>172.57770344938686</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>367375.89822139975</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>776472.3869024337</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>3.113563765782183</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>2.113563765782183</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>27257.269994376395</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.4624948027099762</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>290.0646485861474</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>27257.269994376395</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>299.0063579446161</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$275,A20,'Species'!$U$2:$U$275))</x:f>
-        <x:v>8150097.028531552</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.4624948027099762</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>290.0646485861474</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>7906370.4423365295</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>243726.5861950228</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0308266084890143</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.030826608489014275</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>162760.50852945677</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.195741145191637</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>156.94270916758543</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>162760.50852945677</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>304.6508168868001</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$275,A21,'Species'!$U$2:$U$275))</x:f>
-        <x:v>49585121.88041</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.195741145191637</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>156.94270916758543</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>25544075.15410684</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>24041046.72630316</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.9411594109892043</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.9411594109892042</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>667.5326675757999</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.603877417045631</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>401.677418309175</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>667.5326675757999</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>935.3901984338689</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$275,A22,'Species'!$U$2:$U$275))</x:f>
-        <x:v>624403.5143848173</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.603877417045631</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>401.677418309175</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>268132.79854888405</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>356270.7158359333</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>2.3287099443411825</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>1.3287099443411827</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>5074.6609571516</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.343545907562977</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>220.56972796616128</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>5074.6609571516</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>228.74721413132335</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$275,A23,'Species'!$U$2:$U$275))</x:f>
-        <x:v>1160814.5566094234</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.343545907562977</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>220.56972796616128</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>1119316.5868394282</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>41497.969769995194</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0370743811517806</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.037074381151780696</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>72.60131447789999</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.511424033070786</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>324.65644819132905</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>72.60131447789999</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>325.2767601973804</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$275,A24,'Species'!$U$2:$U$275))</x:f>
-        <x:v>23615.520359442475</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.511424033070786</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>324.65644819132905</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>23570.484892416727</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>45.035467025747494</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0019106720642916</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.0019106720642915853</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>10218.4562770219</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.59</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>389.04514499428046</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>10218.4562770219</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>389.04514499428046</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$275,A25,'Species'!$U$2:$U$275))</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>3975440.8039117004</x:v>
       </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.59</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>389.04514499428046</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
-        <x:v>3975440.8039117004</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G25">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O25">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6849097b52014462"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R168ee17bc00543be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21297,7 +19918,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -21396,7 +20017,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>632611601.862448</x:v>
+        <x:v>441232318.29396504</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -21410,7 +20031,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>632611601.862448</x:v>
+        <x:v>503604725.6354581</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -21424,7 +20045,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-191379283.56848294</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -21438,7 +20059,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-129006876.22698987</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -21449,9 +20070,9 @@
         <x:v>EEZ_076</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -21463,47 +20084,19 @@
         <x:v>EEZ_076</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_076</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_076</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fa64edf16c6411b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ca70935d5b74ec1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21550,7 +20143,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
